--- a/tests/Fixtures/Dossier.de.MaD.IDL.-.C7401.xlsx
+++ b/tests/Fixtures/Dossier.de.MaD.IDL.-.C7401.xlsx
@@ -1970,7 +1970,7 @@
     <t>B.ARON</t>
   </si>
   <si>
-    <t>MAD-OXO-38-C7401</t>
+    <t>OXO-38-C7401</t>
   </si>
   <si>
     <t>L JULIEN</t>
